--- a/dataset/yoruba_sarcasm_extra_compact.xlsx
+++ b/dataset/yoruba_sarcasm_extra_compact.xlsx
@@ -1,9 +1,9 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29819"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29825"/>
   <workbookPr hidePivotFieldList="1"/>
-  <xr:revisionPtr revIDLastSave="816" documentId="8_{CB3F791A-67BD-4899-88B8-2B5492581178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7AD41948-DC69-40F7-BD72-853D9B889E0D}"/>
+  <xr:revisionPtr revIDLastSave="818" documentId="8_{CB3F791A-67BD-4899-88B8-2B5492581178}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8C0CAE4-5DC1-4B2A-A1AD-27FEA296A236}"/>
   <bookViews>
     <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -72,10 +72,10 @@
     <t>A tọrọ owó lọwọ yín, ẹ sì ní kí a wáa gba nílé, èwo ló wáá fa ẹ̀wọ̀n?</t>
   </si>
   <si>
-    <t>Ọmọ náà pupa bíi tááyà ọkọ</t>
-  </si>
-  <si>
-    <t>Ìwọ lo gbọ́n jù nínú gbogbo ọmọ tí ìyá rẹ bí, ọlọ́pọlọ ẹja</t>
+    <t>Ọmọ náà pupa bíi tááyà ọkọ̀</t>
+  </si>
+  <si>
+    <t>Ìwọ lo gbọ́n jù nínúu gbogbo ọmọ tí ìyá rẹ bí, ọlọ́pọlọ ẹja</t>
   </si>
   <si>
     <t>Àìgbọ́fá là ń wòkè, ifá kan kòsí ní párá</t>
